--- a/stocastic-obs/v0/exp4/particle_filter/high_entropy/4_no_1_obs_2_levels_ITI_1/PF_comparisons.xlsx
+++ b/stocastic-obs/v0/exp4/particle_filter/high_entropy/4_no_1_obs_2_levels_ITI_1/PF_comparisons.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lokeshboominathan/Documents/code/auditory-foraging-IRC/stocastic-obs/v0/exp4/particle_filter/high_entropy/4_no_1_obs_2_levels_ITI_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC3C70FE-60DC-294D-95EA-451F487B8131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45AB2747-54B2-7A4F-827F-4338204C0B5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5180" yWindow="1800" windowWidth="28040" windowHeight="17440" xr2:uid="{3ECA16AF-5677-8A4B-B82F-EE82B28D48D0}"/>
+    <workbookView xWindow="2200" yWindow="760" windowWidth="28040" windowHeight="17260" xr2:uid="{3ECA16AF-5677-8A4B-B82F-EE82B28D48D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
   <si>
     <t>Food reward</t>
   </si>
@@ -53,9 +53,6 @@
     <t xml:space="preserve">50 : </t>
   </si>
   <si>
-    <t>350:</t>
-  </si>
-  <si>
     <t>50: 1</t>
   </si>
   <si>
@@ -63,13 +60,22 @@
   </si>
   <si>
     <t>Good guess?</t>
+  </si>
+  <si>
+    <t>350: 1</t>
+  </si>
+  <si>
+    <t>20: 0</t>
+  </si>
+  <si>
+    <t>100: 1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -82,6 +88,14 @@
       <sz val="12"/>
       <color rgb="FF00B050"/>
       <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -110,18 +124,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -440,6 +455,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.6640625" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" style="1"/>
     <col min="5" max="5" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -448,77 +464,90 @@
         <v>0</v>
       </c>
       <c r="E1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="D2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="4"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="2"/>
+      <c r="A3" s="7"/>
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="5"/>
+      <c r="E3" s="4"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="2"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="2"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="2"/>
+      <c r="A6" s="7"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="2"/>
+      <c r="A7" s="7"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="2"/>
+      <c r="A8" s="7"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="2"/>
+      <c r="A9" s="7"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="2"/>
+      <c r="A10" s="7"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="2"/>
+      <c r="A11" s="7"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="2"/>
+      <c r="A12" s="7"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="2"/>
+      <c r="A13" s="7"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="2"/>
+      <c r="A14" s="7"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="2"/>
+      <c r="A15" s="7"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="2"/>
+      <c r="A16" s="7"/>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" s="2"/>
+      <c r="A17" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/stocastic-obs/v0/exp4/particle_filter/high_entropy/4_no_1_obs_2_levels_ITI_1/PF_comparisons.xlsx
+++ b/stocastic-obs/v0/exp4/particle_filter/high_entropy/4_no_1_obs_2_levels_ITI_1/PF_comparisons.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="31">
   <si>
     <t xml:space="preserve">Food reward</t>
   </si>
@@ -110,6 +110,9 @@
   </si>
   <si>
     <t xml:space="preserve">env_param = [0.0, *, 6.8511, 1, -5000, 0]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">env_param = [0.0, *, 3.4255, 1, -5000, 0]</t>
   </si>
 </sst>
 </file>
@@ -216,7 +219,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -249,16 +252,24 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -338,7 +349,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr defaultColWidth="10.50390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.66"/>
@@ -440,53 +451,56 @@
       <c r="A17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="8" t="n">
+      <c r="B18" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="8" t="n">
+      <c r="C18" s="9" t="n">
         <v>0.0104788442565035</v>
       </c>
-      <c r="D18" s="8" t="n">
+      <c r="D18" s="9" t="n">
         <v>2305.125</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="8" t="n">
+      <c r="B19" s="9" t="n">
         <v>2.18918918918919</v>
       </c>
-      <c r="C19" s="8" t="n">
+      <c r="C19" s="9" t="n">
         <v>0.032820672635052</v>
       </c>
-      <c r="D19" s="8" t="n">
+      <c r="D19" s="9" t="n">
         <v>361.675675675676</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="9" t="s">
+      <c r="A24" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="9" t="n">
+      <c r="A25" s="8" t="n">
         <v>20</v>
       </c>
       <c r="B25" s="1" t="n">
@@ -500,7 +514,7 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="9" t="n">
+      <c r="A26" s="8" t="n">
         <v>50</v>
       </c>
       <c r="B26" s="1" t="n">
@@ -514,7 +528,7 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="9" t="n">
+      <c r="A27" s="8" t="n">
         <v>100</v>
       </c>
       <c r="B27" s="1" t="n">
@@ -528,7 +542,7 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="9" t="n">
+      <c r="A28" s="8" t="n">
         <v>350</v>
       </c>
       <c r="B28" s="1" t="n">
@@ -542,7 +556,7 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="9" t="n">
+      <c r="A29" s="8" t="n">
         <v>500</v>
       </c>
       <c r="B29" s="1" t="n">
@@ -556,7 +570,7 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="9" t="n">
+      <c r="A30" s="8" t="n">
         <v>1000</v>
       </c>
       <c r="B30" s="1" t="n">
@@ -575,25 +589,25 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="D36" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="9" t="n">
+      <c r="A37" s="8" t="n">
         <v>100</v>
       </c>
       <c r="B37" s="1" t="n">
@@ -607,39 +621,39 @@
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="9" t="n">
+      <c r="A38" s="8" t="n">
         <v>350</v>
       </c>
-      <c r="B38" s="8" t="n">
+      <c r="B38" s="11" t="n">
         <v>4.31372549019608</v>
       </c>
-      <c r="C38" s="8" t="n">
+      <c r="C38" s="11" t="n">
         <v>0.0083430285626968</v>
       </c>
-      <c r="D38" s="8" t="n">
+      <c r="D38" s="11" t="n">
         <v>923.235294117647</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="C42" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D42" s="9" t="s">
+      <c r="D42" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="9" t="n">
+      <c r="A43" s="8" t="n">
         <v>-3</v>
       </c>
       <c r="B43" s="1" t="n">
@@ -653,53 +667,53 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="9" t="n">
+      <c r="A44" s="8" t="n">
         <v>-1</v>
       </c>
-      <c r="B44" s="8" t="n">
+      <c r="B44" s="11" t="n">
         <v>3.98039215686275</v>
       </c>
-      <c r="C44" s="8" t="n">
+      <c r="C44" s="11" t="n">
         <v>0.00811695156729735</v>
       </c>
-      <c r="D44" s="8" t="n">
+      <c r="D44" s="11" t="n">
         <v>812.450980392157</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="9" t="n">
+      <c r="A45" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="B45" s="8" t="n">
+      <c r="B45" s="11" t="n">
         <v>4.31372549019608</v>
       </c>
-      <c r="C45" s="8" t="n">
+      <c r="C45" s="11" t="n">
         <v>0.0083430285626968</v>
       </c>
-      <c r="D45" s="8" t="n">
+      <c r="D45" s="11" t="n">
         <v>923.235294117647</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="9" t="s">
+      <c r="B48" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="9" t="s">
+      <c r="B49" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C49" s="9" t="s">
+      <c r="C49" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D49" s="9" t="s">
+      <c r="D49" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="9" t="n">
+      <c r="A50" s="8" t="n">
         <v>-3</v>
       </c>
       <c r="B50" s="1" t="n">
@@ -713,7 +727,7 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="9" t="n">
+      <c r="A51" s="8" t="n">
         <v>0</v>
       </c>
       <c r="B51" s="1" t="n">
@@ -727,159 +741,159 @@
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="9"/>
+      <c r="A52" s="8"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="9" t="s">
+      <c r="B54" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="10"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="9" t="s">
+      <c r="B55" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C55" s="9" t="s">
+      <c r="C55" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D55" s="9" t="s">
+      <c r="D55" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="9" t="n">
+      <c r="A56" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="B56" s="8" t="n">
+      <c r="B56" s="11" t="n">
         <v>5.07843137254902</v>
       </c>
-      <c r="C56" s="8" t="n">
+      <c r="C56" s="11" t="n">
         <v>0.00764128431173118</v>
       </c>
-      <c r="D56" s="8" t="n">
+      <c r="D56" s="11" t="n">
         <v>1135.8431372549</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="9" t="n">
+      <c r="A57" s="8" t="n">
         <v>350</v>
       </c>
-      <c r="B57" s="8" t="n">
+      <c r="B57" s="11" t="n">
         <v>8.25490196078431</v>
       </c>
-      <c r="C57" s="8" t="n">
+      <c r="C57" s="11" t="n">
         <v>0.00694726649004607</v>
       </c>
-      <c r="D57" s="8" t="n">
+      <c r="D57" s="11" t="n">
         <v>1829</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="10"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C61" s="9" t="s">
+      <c r="C61" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D61" s="9" t="s">
+      <c r="D61" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="9" t="s">
+      <c r="A62" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B62" s="8" t="n">
+      <c r="B62" s="11" t="n">
         <v>5.92156862745098</v>
       </c>
-      <c r="C62" s="8" t="n">
+      <c r="C62" s="11" t="n">
         <v>0.00801635534047921</v>
       </c>
-      <c r="D62" s="8" t="n">
+      <c r="D62" s="11" t="n">
         <v>1236.52941176471</v>
       </c>
-      <c r="E62" s="10" t="n">
+      <c r="E62" s="9" t="n">
         <v>0.01</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="9" t="s">
+      <c r="A63" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B63" s="8" t="n">
+      <c r="B63" s="11" t="n">
         <v>4.86274509803922</v>
       </c>
-      <c r="C63" s="8" t="n">
+      <c r="C63" s="11" t="n">
         <v>0.00931977982637726</v>
       </c>
-      <c r="D63" s="8" t="n">
+      <c r="D63" s="11" t="n">
         <v>1090.82352941176</v>
       </c>
-      <c r="E63" s="10" t="n">
+      <c r="E63" s="9" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="9" t="s">
+      <c r="A64" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B64" s="8" t="n">
+      <c r="B64" s="11" t="n">
         <v>6.76470588235294</v>
       </c>
-      <c r="C64" s="8" t="n">
+      <c r="C64" s="11" t="n">
         <v>0.00672699499925887</v>
       </c>
-      <c r="D64" s="8" t="n">
+      <c r="D64" s="11" t="n">
         <v>1447.56862745098</v>
       </c>
-      <c r="E64" s="10" t="n">
+      <c r="E64" s="9" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="9" t="s">
+      <c r="A65" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B65" s="8" t="n">
+      <c r="B65" s="11" t="n">
         <v>7.19607843137255</v>
       </c>
-      <c r="C65" s="8" t="n">
+      <c r="C65" s="11" t="n">
         <v>0.00903615178950955</v>
       </c>
-      <c r="D65" s="8" t="n">
+      <c r="D65" s="11" t="n">
         <v>1536.35294117647</v>
       </c>
-      <c r="E65" s="9" t="n">
+      <c r="E65" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="9" t="s">
+      <c r="A66" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B66" s="8" t="n">
+      <c r="B66" s="11" t="n">
         <v>8.25490196078431</v>
       </c>
-      <c r="C66" s="8" t="n">
+      <c r="C66" s="11" t="n">
         <v>0.00694726649004607</v>
       </c>
-      <c r="D66" s="8" t="n">
+      <c r="D66" s="11" t="n">
         <v>1829</v>
       </c>
-      <c r="E66" s="10" t="n">
+      <c r="E66" s="9" t="n">
         <v>1.45960311115695</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="9" t="s">
+      <c r="A67" s="8" t="s">
         <v>28</v>
       </c>
       <c r="B67" s="1" t="n">
@@ -891,43 +905,107 @@
       <c r="D67" s="1" t="n">
         <v>842.450980392157</v>
       </c>
-      <c r="E67" s="10" t="n">
+      <c r="E67" s="9" t="n">
         <v>2.84785875549424</v>
       </c>
     </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="8"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="8"/>
+    </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="9" t="s">
+      <c r="B71" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C71" s="9"/>
-      <c r="D71" s="9"/>
+      <c r="C71" s="10"/>
+      <c r="D71" s="10"/>
+      <c r="E71" s="8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="9" t="s">
+      <c r="B72" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C72" s="9" t="s">
+      <c r="C72" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D72" s="9" t="s">
+      <c r="D72" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="9" t="n">
+      <c r="A73" s="8" t="n">
         <v>100</v>
       </c>
+      <c r="B73" s="12" t="n">
+        <v>4.64705882352941</v>
+      </c>
+      <c r="C73" s="12" t="n">
+        <v>0.00668323684472944</v>
+      </c>
+      <c r="D73" s="12" t="n">
+        <v>985.901960784314</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="9" t="n">
+      <c r="A74" s="8" t="n">
         <v>350</v>
       </c>
-      <c r="B74" s="8"/>
-      <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
+      <c r="B74" s="12" t="n">
+        <v>5.05882352941176</v>
+      </c>
+      <c r="C74" s="12" t="n">
+        <v>0.00618558919880052</v>
+      </c>
+      <c r="D74" s="12" t="n">
+        <v>1175.80392156863</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E76" s="8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B77" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C77" s="10"/>
+      <c r="D77" s="10"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B78" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B79" s="12"/>
+      <c r="C79" s="12"/>
+      <c r="D79" s="12"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="8" t="n">
+        <v>350</v>
+      </c>
+      <c r="B80" s="12"/>
+      <c r="C80" s="12"/>
+      <c r="D80" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A2:A17"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B35:D35"/>
@@ -936,6 +1014,7 @@
     <mergeCell ref="B54:D54"/>
     <mergeCell ref="B60:D60"/>
     <mergeCell ref="B71:D71"/>
+    <mergeCell ref="B77:D77"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/stocastic-obs/v0/exp4/particle_filter/high_entropy/4_no_1_obs_2_levels_ITI_1/PF_comparisons.xlsx
+++ b/stocastic-obs/v0/exp4/particle_filter/high_entropy/4_no_1_obs_2_levels_ITI_1/PF_comparisons.xlsx
@@ -349,7 +349,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E87"/>
   <sheetFormatPr defaultColWidth="10.50390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.66"/>
@@ -455,13 +455,13 @@
         <v>11</v>
       </c>
       <c r="B18" s="9" t="n">
-        <v>8</v>
+        <v>9.8</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>0.0104788442565035</v>
+        <v>0.00743572324799274</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>2305.125</v>
+        <v>2965.5</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -634,69 +634,51 @@
         <v>923.235294117647</v>
       </c>
     </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B39" s="12" t="n">
+        <v>11.6078431372549</v>
+      </c>
+      <c r="C39" s="12" t="n">
+        <v>0.00652389003200966</v>
+      </c>
+      <c r="D39" s="12" t="n">
+        <v>2778.27450980392</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="B40" s="12" t="n">
+        <v>9.23529411764706</v>
+      </c>
+      <c r="C40" s="12" t="n">
+        <v>0.00734532501339011</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>2029.58823529412</v>
+      </c>
+    </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="8" t="n">
-        <v>-3</v>
-      </c>
-      <c r="B43" s="1" t="n">
-        <v>4.11764705882353</v>
-      </c>
-      <c r="C43" s="1" t="n">
-        <v>0.00681639853184622</v>
-      </c>
-      <c r="D43" s="1" t="n">
-        <v>842.450980392157</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="B44" s="11" t="n">
-        <v>3.98039215686275</v>
-      </c>
-      <c r="C44" s="11" t="n">
-        <v>0.00811695156729735</v>
-      </c>
-      <c r="D44" s="11" t="n">
-        <v>812.450980392157</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="B45" s="11" t="n">
-        <v>4.31372549019608</v>
-      </c>
-      <c r="C45" s="11" t="n">
-        <v>0.0083430285626968</v>
-      </c>
-      <c r="D45" s="11" t="n">
-        <v>923.235294117647</v>
+      <c r="A41" s="8" t="n">
+        <v>50000</v>
+      </c>
+      <c r="B41" s="12" t="n">
+        <v>10.7058823529412</v>
+      </c>
+      <c r="C41" s="12" t="n">
+        <v>0.00551196962742907</v>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>2527.11764705882</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C48" s="10"/>
       <c r="D48" s="10"/>
@@ -717,304 +699,374 @@
         <v>-3</v>
       </c>
       <c r="B50" s="1" t="n">
-        <v>8.66666666666667</v>
+        <v>4.11764705882353</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>0.00456714269628052</v>
+        <v>0.00681639853184622</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>2082.29411764706</v>
+        <v>842.450980392157</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="B51" s="11" t="n">
+        <v>3.98039215686275</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>0.00811695156729735</v>
+      </c>
+      <c r="D51" s="11" t="n">
+        <v>812.450980392157</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="B51" s="1" t="n">
-        <v>7.6078431372549</v>
-      </c>
-      <c r="C51" s="1" t="n">
-        <v>0.00646939246964509</v>
-      </c>
-      <c r="D51" s="1" t="n">
-        <v>1660.64705882353</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="8"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C54" s="10"/>
-      <c r="D54" s="10"/>
+      <c r="B52" s="11" t="n">
+        <v>4.31372549019608</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>0.0083430285626968</v>
+      </c>
+      <c r="D52" s="11" t="n">
+        <v>923.235294117647</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C55" s="10"/>
+      <c r="D55" s="10"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C55" s="8" t="s">
+      <c r="C56" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D55" s="8" t="s">
+      <c r="D56" s="8" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="B56" s="11" t="n">
-        <v>5.07843137254902</v>
-      </c>
-      <c r="C56" s="11" t="n">
-        <v>0.00764128431173118</v>
-      </c>
-      <c r="D56" s="11" t="n">
-        <v>1135.8431372549</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="n">
+        <v>-3</v>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>8.66666666666667</v>
+      </c>
+      <c r="C57" s="1" t="n">
+        <v>0.00456714269628052</v>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>2082.29411764706</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>7.6078431372549</v>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>0.00646939246964509</v>
+      </c>
+      <c r="D58" s="1" t="n">
+        <v>1660.64705882353</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="8"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C61" s="10"/>
+      <c r="D61" s="10"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B63" s="11" t="n">
+        <v>5.07843137254902</v>
+      </c>
+      <c r="C63" s="11" t="n">
+        <v>0.00764128431173118</v>
+      </c>
+      <c r="D63" s="11" t="n">
+        <v>1135.8431372549</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="8" t="n">
         <v>350</v>
       </c>
-      <c r="B57" s="11" t="n">
+      <c r="B64" s="11" t="n">
         <v>8.25490196078431</v>
       </c>
-      <c r="C57" s="11" t="n">
+      <c r="C64" s="11" t="n">
         <v>0.00694726649004607</v>
       </c>
-      <c r="D57" s="11" t="n">
+      <c r="D64" s="11" t="n">
         <v>1829</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="10" t="s">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C60" s="10"/>
-      <c r="D60" s="10"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="8" t="s">
+      <c r="C67" s="10"/>
+      <c r="D67" s="10"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B68" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C61" s="8" t="s">
+      <c r="C68" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D61" s="8" t="s">
+      <c r="D68" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="8" t="s">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B62" s="11" t="n">
+      <c r="B69" s="11" t="n">
         <v>5.92156862745098</v>
       </c>
-      <c r="C62" s="11" t="n">
+      <c r="C69" s="11" t="n">
         <v>0.00801635534047921</v>
       </c>
-      <c r="D62" s="11" t="n">
+      <c r="D69" s="11" t="n">
         <v>1236.52941176471</v>
       </c>
-      <c r="E62" s="9" t="n">
+      <c r="E69" s="9" t="n">
         <v>0.01</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="8" t="s">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B63" s="11" t="n">
+      <c r="B70" s="11" t="n">
         <v>4.86274509803922</v>
       </c>
-      <c r="C63" s="11" t="n">
+      <c r="C70" s="11" t="n">
         <v>0.00931977982637726</v>
       </c>
-      <c r="D63" s="11" t="n">
+      <c r="D70" s="11" t="n">
         <v>1090.82352941176</v>
       </c>
-      <c r="E63" s="9" t="n">
+      <c r="E70" s="9" t="n">
         <v>0.1</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="8" t="s">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B64" s="11" t="n">
+      <c r="B71" s="11" t="n">
         <v>6.76470588235294</v>
       </c>
-      <c r="C64" s="11" t="n">
+      <c r="C71" s="11" t="n">
         <v>0.00672699499925887</v>
       </c>
-      <c r="D64" s="11" t="n">
+      <c r="D71" s="11" t="n">
         <v>1447.56862745098</v>
       </c>
-      <c r="E64" s="9" t="n">
+      <c r="E71" s="9" t="n">
         <v>0.5</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="8" t="s">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B65" s="11" t="n">
+      <c r="B72" s="11" t="n">
         <v>7.19607843137255</v>
       </c>
-      <c r="C65" s="11" t="n">
+      <c r="C72" s="11" t="n">
         <v>0.00903615178950955</v>
       </c>
-      <c r="D65" s="11" t="n">
+      <c r="D72" s="11" t="n">
         <v>1536.35294117647</v>
       </c>
-      <c r="E65" s="8" t="n">
+      <c r="E72" s="8" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="8" t="s">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B66" s="11" t="n">
+      <c r="B73" s="11" t="n">
         <v>8.25490196078431</v>
       </c>
-      <c r="C66" s="11" t="n">
+      <c r="C73" s="11" t="n">
         <v>0.00694726649004607</v>
       </c>
-      <c r="D66" s="11" t="n">
+      <c r="D73" s="11" t="n">
         <v>1829</v>
       </c>
-      <c r="E66" s="9" t="n">
+      <c r="E73" s="9" t="n">
         <v>1.45960311115695</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="8" t="s">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B74" s="1" t="n">
         <v>4.11764705882353</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C74" s="1" t="n">
         <v>0.00681639853184622</v>
       </c>
-      <c r="D67" s="1" t="n">
+      <c r="D74" s="1" t="n">
         <v>842.450980392157</v>
       </c>
-      <c r="E67" s="9" t="n">
+      <c r="E74" s="9" t="n">
         <v>2.84785875549424</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="8"/>
-      <c r="B68" s="12"/>
-      <c r="C68" s="12"/>
-      <c r="D68" s="12"/>
-      <c r="E68" s="8"/>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="10" t="s">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="8"/>
+      <c r="B75" s="11"/>
+      <c r="C75" s="11"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="8"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B78" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C71" s="10"/>
-      <c r="D71" s="10"/>
-      <c r="E71" s="8" t="n">
+      <c r="C78" s="10"/>
+      <c r="D78" s="10"/>
+      <c r="E78" s="8" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="8" t="s">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B79" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C72" s="8" t="s">
+      <c r="C79" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D72" s="8" t="s">
+      <c r="D79" s="8" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="B73" s="12" t="n">
-        <v>4.64705882352941</v>
-      </c>
-      <c r="C73" s="12" t="n">
-        <v>0.00668323684472944</v>
-      </c>
-      <c r="D73" s="12" t="n">
-        <v>985.901960784314</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="8" t="n">
-        <v>350</v>
-      </c>
-      <c r="B74" s="12" t="n">
-        <v>5.05882352941176</v>
-      </c>
-      <c r="C74" s="12" t="n">
-        <v>0.00618558919880052</v>
-      </c>
-      <c r="D74" s="12" t="n">
-        <v>1175.80392156863</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E76" s="8" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B77" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C77" s="10"/>
-      <c r="D77" s="10"/>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B78" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D78" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="B79" s="12"/>
-      <c r="C79" s="12"/>
-      <c r="D79" s="12"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B80" s="11" t="n">
+        <v>5.82352941176471</v>
+      </c>
+      <c r="C80" s="11" t="n">
+        <v>0.00691825175559639</v>
+      </c>
+      <c r="D80" s="11" t="n">
+        <v>1261.29411764706</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="8" t="n">
         <v>350</v>
       </c>
-      <c r="B80" s="12"/>
-      <c r="C80" s="12"/>
-      <c r="D80" s="12"/>
+      <c r="B81" s="11" t="n">
+        <v>4.80392156862745</v>
+      </c>
+      <c r="C81" s="11" t="n">
+        <v>0.00615828510275328</v>
+      </c>
+      <c r="D81" s="11" t="n">
+        <v>987.882352941177</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B84" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C84" s="10"/>
+      <c r="D84" s="10"/>
+      <c r="E84" s="8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B85" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B86" s="11" t="n">
+        <v>5.66666666666667</v>
+      </c>
+      <c r="C86" s="11" t="n">
+        <v>0.00642317047868657</v>
+      </c>
+      <c r="D86" s="11" t="n">
+        <v>1165.41176470588</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="8" t="n">
+        <v>350</v>
+      </c>
+      <c r="B87" s="11" t="n">
+        <v>5.80392156862745</v>
+      </c>
+      <c r="C87" s="11" t="n">
+        <v>0.00590907991302974</v>
+      </c>
+      <c r="D87" s="11" t="n">
+        <v>1354.96078431373</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A2:A17"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B41:D41"/>
     <mergeCell ref="B48:D48"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B71:D71"/>
-    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B84:D84"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/stocastic-obs/v0/exp4/particle_filter/high_entropy/4_no_1_obs_2_levels_ITI_1/PF_comparisons.xlsx
+++ b/stocastic-obs/v0/exp4/particle_filter/high_entropy/4_no_1_obs_2_levels_ITI_1/PF_comparisons.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="32">
   <si>
     <t xml:space="preserve">Food reward</t>
   </si>
@@ -113,6 +113,9 @@
   </si>
   <si>
     <t xml:space="preserve">env_param = [0.0, *, 3.4255, 1, -5000, 0]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">env_param =  [0, *, .08, .25, 0, 0]</t>
   </si>
 </sst>
 </file>
@@ -129,7 +132,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -152,7 +154,6 @@
       <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -160,7 +161,6 @@
       <color rgb="FF00B050"/>
       <name val="Calibri (Body)"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -168,7 +168,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -349,7 +348,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr defaultColWidth="10.50390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.66"/>
@@ -1056,8 +1055,57 @@
         <v>1354.96078431373</v>
       </c>
     </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B92" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C92" s="10"/>
+      <c r="D92" s="10"/>
+      <c r="E92" s="9" t="n">
+        <v>2.84785875549424</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B93" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B94" s="12" t="n">
+        <v>1.64705882352941</v>
+      </c>
+      <c r="C94" s="12" t="n">
+        <v>0.00620256612272322</v>
+      </c>
+      <c r="D94" s="12" t="n">
+        <v>274.21568627451</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="8" t="n">
+        <v>350</v>
+      </c>
+      <c r="B95" s="12" t="n">
+        <v>5.7843137254902</v>
+      </c>
+      <c r="C95" s="12" t="n">
+        <v>0.00959599771752437</v>
+      </c>
+      <c r="D95" s="12" t="n">
+        <v>1171.56862745098</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A2:A17"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B35:D35"/>
@@ -1067,6 +1115,7 @@
     <mergeCell ref="B67:D67"/>
     <mergeCell ref="B78:D78"/>
     <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B92:D92"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
